--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A653DD-0324-43DE-9B6E-2CDDE8F6C02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002F63CC-6C9D-4F6F-806D-BFC37844DD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="175">
   <si>
     <t>Fecha</t>
   </si>
@@ -533,39 +533,9 @@
     <t>Ubicaciones registradas</t>
   </si>
   <si>
-    <t>Sede Villa - Martes de la Semana de Ingeniería</t>
-  </si>
-  <si>
-    <t>Requerimientos :</t>
-  </si>
-  <si>
-    <t>• 3 toldos con 3 puntos de luz.</t>
-  </si>
-  <si>
-    <t>• 3 mesas con mantel.</t>
-  </si>
-  <si>
-    <t>• 6 sillas (2 por toldo).</t>
-  </si>
-  <si>
-    <t>• 1 televisor.</t>
-  </si>
-  <si>
-    <t>Sede Villa - Feria Empresarial</t>
-  </si>
-  <si>
     <t>Sede Villa – Jardin Lote 28</t>
   </si>
   <si>
-    <t>• 8 toldos.</t>
-  </si>
-  <si>
-    <t>• 8 mesas con mantel.</t>
-  </si>
-  <si>
-    <t>• 16 sillas (2 por mesa).</t>
-  </si>
-  <si>
     <t>MEDICINA HUMANA</t>
   </si>
   <si>
@@ -575,40 +545,67 @@
     <t>Clínica de Simulación</t>
   </si>
   <si>
-    <t>• 5 mesas</t>
-  </si>
-  <si>
-    <t>• 25 sillas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no especifica </t>
-  </si>
-  <si>
     <t>Hall del Pabellón N</t>
   </si>
   <si>
-    <t>Por favor retirar muebles del hall y colocar: 9:30 am a 12:00 pm</t>
-  </si>
-  <si>
-    <t>- 60 sillas en formato auditorio.</t>
-  </si>
-  <si>
-    <t>-  TV en rack al fondo  - la del pabellón L.</t>
-  </si>
-  <si>
-    <t>- Bandera de Científica y del Perú</t>
-  </si>
-  <si>
-    <t>- Podio de Científica</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campaña Certijoven </t>
   </si>
   <si>
-    <t>Pabellon I</t>
-  </si>
-  <si>
-    <t>solicitamos su apoyo para habilitar una mesa con mantel + dos sillas en el hall de pasillo del pabellón I. Para la socialización del aplicativo ApliJoven de MINEDU que se realizará el lunes16 de junio de 8:30 am a 2:00</t>
+    <t>Gaming Tournament</t>
+  </si>
+  <si>
+    <t>Auditorio O203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARRERA DE ENFERMERIA </t>
+  </si>
+  <si>
+    <t>Campaña por el día nacional de la prueba rápida del VIH</t>
+  </si>
+  <si>
+    <t>Jardín de pabellón N</t>
+  </si>
+  <si>
+    <t>AREA DE CCBB</t>
+  </si>
+  <si>
+    <t>Coloquio Internacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pabellon I - pasillo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 mesas con mantel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 mesas / 25 sillas </t>
+  </si>
+  <si>
+    <t>60 sillas / tv con rack / banderas de cientifica y peru / podium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 mesa con mantel / 2 sillas </t>
+  </si>
+  <si>
+    <t>5 toldos / 6 mesas / 24 sillas / 6 manteles / puntos de energia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 sillones / 2 mesas de registro / 2 sillas / 3 mesas para catering / 3 manteles / totem colloquio / 73 sillas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 toldos / 3 mesas  / 6 sillas / 1televisor </t>
+  </si>
+  <si>
+    <t>Semana de Ingeniería</t>
+  </si>
+  <si>
+    <t>Feria Empresarial</t>
+  </si>
+  <si>
+    <t>8 toldos / 8 mesas / 8 manteles / 16 sillas (2 por mesas)</t>
+  </si>
+  <si>
+    <t>INGENIERA ACUICOLA</t>
   </si>
 </sst>
 </file>
@@ -618,7 +615,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -645,19 +642,8 @@
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF991B1B"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Carlito"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -686,26 +672,8 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E6F5"/>
-        <bgColor rgb="FFC0E6F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61CBF3"/>
-        <bgColor rgb="FFC0E6F5"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="18">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -750,159 +718,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -948,123 +768,27 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <font>
         <b/>
@@ -1120,6 +844,9 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1139,7 +866,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Área Solicitante"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Evento / Actividad"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ubicación"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Requerimientos"/>
@@ -1300,18 +1027,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" style="20" customWidth="1"/>
     <col min="5" max="6" width="34" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="5.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26.1" customHeight="1">
@@ -1356,7 +1084,7 @@
       <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1388,7 +1116,7 @@
       <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="17" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -1420,7 +1148,7 @@
       <c r="C4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="17" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -1452,7 +1180,7 @@
       <c r="C5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="17" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -1484,7 +1212,7 @@
       <c r="C6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="17"/>
       <c r="E6" s="2" t="s">
         <v>37</v>
       </c>
@@ -1514,7 +1242,7 @@
       <c r="C7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="17"/>
       <c r="E7" s="2" t="s">
         <v>42</v>
       </c>
@@ -1542,7 +1270,7 @@
       <c r="C8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="17" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -1574,7 +1302,7 @@
       <c r="C9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="17" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -1606,7 +1334,7 @@
       <c r="C10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="17" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -1638,7 +1366,7 @@
       <c r="C11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="17" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -1670,7 +1398,7 @@
       <c r="C12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="17" t="s">
         <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -1702,7 +1430,7 @@
       <c r="C13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -1734,7 +1462,7 @@
       <c r="C14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="17" t="s">
         <v>74</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -1766,7 +1494,7 @@
       <c r="C15" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="18" t="s">
         <v>78</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -1798,7 +1526,7 @@
       <c r="C16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="18" t="s">
         <v>78</v>
       </c>
       <c r="E16" s="8" t="s">
@@ -1830,7 +1558,7 @@
       <c r="C17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -1862,7 +1590,7 @@
       <c r="C18" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="12" t="s">
@@ -1894,7 +1622,7 @@
       <c r="C19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -1926,7 +1654,7 @@
       <c r="C20" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="12" t="s">
@@ -1958,7 +1686,7 @@
       <c r="C21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -1990,7 +1718,7 @@
       <c r="C22" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="12" t="s">
@@ -2022,7 +1750,7 @@
       <c r="C23" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="12" t="s">
@@ -2054,7 +1782,7 @@
       <c r="C24" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -2086,7 +1814,7 @@
       <c r="C25" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -2118,7 +1846,7 @@
       <c r="C26" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -2150,7 +1878,7 @@
       <c r="C27" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -2182,7 +1910,7 @@
       <c r="C28" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="12" t="s">
@@ -2214,7 +1942,7 @@
       <c r="C29" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="12" t="s">
@@ -2246,7 +1974,7 @@
       <c r="C30" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="12" t="s">
@@ -2278,7 +2006,7 @@
       <c r="C31" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -2310,7 +2038,7 @@
       <c r="C32" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="12" t="s">
@@ -2342,7 +2070,7 @@
       <c r="C33" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="12" t="s">
@@ -2374,7 +2102,7 @@
       <c r="C34" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E34" s="12" t="s">
@@ -2406,7 +2134,7 @@
       <c r="C35" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E35" s="12" t="s">
@@ -2438,7 +2166,7 @@
       <c r="C36" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="12" t="s">
@@ -2470,7 +2198,7 @@
       <c r="C37" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E37" s="12" t="s">
@@ -2502,7 +2230,7 @@
       <c r="C38" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="12" t="s">
@@ -2534,7 +2262,7 @@
       <c r="C39" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="12" t="s">
@@ -2566,7 +2294,7 @@
       <c r="C40" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="12" t="s">
@@ -2598,7 +2326,7 @@
       <c r="C41" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="12" t="s">
@@ -2630,7 +2358,7 @@
       <c r="C42" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="12" t="s">
@@ -2662,7 +2390,7 @@
       <c r="C43" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="12" t="s">
@@ -2694,7 +2422,7 @@
       <c r="C44" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="12" t="s">
@@ -2726,7 +2454,7 @@
       <c r="C45" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E45" s="12" t="s">
@@ -2758,7 +2486,7 @@
       <c r="C46" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="12" t="s">
@@ -2790,7 +2518,7 @@
       <c r="C47" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="12" t="s">
@@ -2822,7 +2550,7 @@
       <c r="C48" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="12" t="s">
@@ -2854,7 +2582,7 @@
       <c r="C49" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="12" t="s">
@@ -2886,7 +2614,7 @@
       <c r="C50" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="12" t="s">
@@ -2918,7 +2646,7 @@
       <c r="C51" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="12" t="s">
@@ -2950,7 +2678,7 @@
       <c r="C52" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="12" t="s">
@@ -2982,7 +2710,7 @@
       <c r="C53" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="12" t="s">
@@ -3014,7 +2742,7 @@
       <c r="C54" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="12" t="s">
@@ -3046,7 +2774,7 @@
       <c r="C55" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="12" t="s">
@@ -3078,7 +2806,7 @@
       <c r="C56" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="12" t="s">
@@ -3110,7 +2838,7 @@
       <c r="C57" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="12" t="s">
@@ -3142,7 +2870,7 @@
       <c r="C58" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="12" t="s">
@@ -3174,7 +2902,7 @@
       <c r="C59" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="12" t="s">
@@ -3206,7 +2934,7 @@
       <c r="C60" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="12" t="s">
@@ -3238,7 +2966,7 @@
       <c r="C61" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="12" t="s">
@@ -3270,7 +2998,7 @@
       <c r="C62" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="12" t="s">
@@ -3302,7 +3030,7 @@
       <c r="C63" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="12" t="s">
@@ -3324,7 +3052,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" ht="14.25" customHeight="1">
       <c r="A64" s="16" t="s">
         <v>94</v>
       </c>
@@ -3334,7 +3062,7 @@
       <c r="C64" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="12" t="s">
@@ -3366,7 +3094,7 @@
       <c r="C65" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="12" t="s">
@@ -3398,7 +3126,7 @@
       <c r="C66" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="12" t="s">
@@ -3430,7 +3158,7 @@
       <c r="C67" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E67" s="12" t="s">
@@ -3462,7 +3190,7 @@
       <c r="C68" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E68" s="12" t="s">
@@ -3494,7 +3222,7 @@
       <c r="C69" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E69" s="12" t="s">
@@ -3526,7 +3254,7 @@
       <c r="C70" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D70" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="12" t="s">
@@ -3558,7 +3286,7 @@
       <c r="C71" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E71" s="12" t="s">
@@ -3590,7 +3318,7 @@
       <c r="C72" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="12" t="s">
@@ -3622,7 +3350,7 @@
       <c r="C73" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="12" t="s">
@@ -3654,7 +3382,7 @@
       <c r="C74" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="12" t="s">
@@ -3686,7 +3414,7 @@
       <c r="C75" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D75" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="12" t="s">
@@ -3718,7 +3446,7 @@
       <c r="C76" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D76" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="12" t="s">
@@ -3750,7 +3478,7 @@
       <c r="C77" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D77" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E77" s="12" t="s">
@@ -3782,7 +3510,7 @@
       <c r="C78" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="12" t="s">
@@ -3814,7 +3542,7 @@
       <c r="C79" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="12" t="s">
@@ -3846,7 +3574,7 @@
       <c r="C80" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="12" t="s">
@@ -3878,7 +3606,7 @@
       <c r="C81" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="12" t="s">
@@ -3910,7 +3638,7 @@
       <c r="C82" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E82" s="12" t="s">
@@ -3942,7 +3670,7 @@
       <c r="C83" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E83" s="12" t="s">
@@ -3974,7 +3702,7 @@
       <c r="C84" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="12" t="s">
@@ -4006,7 +3734,7 @@
       <c r="C85" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E85" s="12" t="s">
@@ -4038,7 +3766,7 @@
       <c r="C86" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="12" t="s">
@@ -4070,7 +3798,7 @@
       <c r="C87" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E87" s="12" t="s">
@@ -4102,7 +3830,7 @@
       <c r="C88" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E88" s="12" t="s">
@@ -4134,7 +3862,7 @@
       <c r="C89" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E89" s="12" t="s">
@@ -4166,7 +3894,7 @@
       <c r="C90" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E90" s="12" t="s">
@@ -4198,7 +3926,7 @@
       <c r="C91" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E91" s="12" t="s">
@@ -4230,7 +3958,7 @@
       <c r="C92" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E92" s="12" t="s">
@@ -4262,7 +3990,7 @@
       <c r="C93" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D93" s="12" t="s">
+      <c r="D93" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E93" s="12" t="s">
@@ -4294,7 +4022,7 @@
       <c r="C94" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D94" s="12" t="s">
+      <c r="D94" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="12" t="s">
@@ -4326,7 +4054,7 @@
       <c r="C95" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E95" s="12" t="s">
@@ -4358,7 +4086,7 @@
       <c r="C96" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D96" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E96" s="12" t="s">
@@ -4390,7 +4118,7 @@
       <c r="C97" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D97" s="12" t="s">
+      <c r="D97" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E97" s="12" t="s">
@@ -4422,7 +4150,7 @@
       <c r="C98" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D98" s="12" t="s">
+      <c r="D98" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E98" s="12" t="s">
@@ -4454,7 +4182,7 @@
       <c r="C99" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D99" s="12" t="s">
+      <c r="D99" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="12" t="s">
@@ -4486,7 +4214,7 @@
       <c r="C100" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D100" s="12" t="s">
+      <c r="D100" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="12" t="s">
@@ -4518,7 +4246,7 @@
       <c r="C101" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D101" s="12" t="s">
+      <c r="D101" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="12" t="s">
@@ -4540,517 +4268,360 @@
         <v>86</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
-      <c r="A102" s="31">
+    <row r="102" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A102" s="16">
         <v>46182</v>
       </c>
-      <c r="B102" s="35">
+      <c r="B102" s="15">
         <v>0.47152777777777777</v>
       </c>
-      <c r="C102" s="39" t="s">
+      <c r="C102" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D102" s="43">
+      <c r="D102" s="19">
         <v>81688</v>
       </c>
-      <c r="E102" s="47" t="s">
+      <c r="E102" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H102" t="s">
+        <v>17</v>
+      </c>
+      <c r="I102" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A103" s="16">
+        <v>46186</v>
+      </c>
+      <c r="B103" s="15">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D103" s="19">
+        <v>81685</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="F103" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="F102" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="G102" s="21" t="s">
+      <c r="G103" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="H103" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J103" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A104" s="16">
+        <v>46190</v>
+      </c>
+      <c r="B104" s="15">
+        <v>0.77152777777777781</v>
+      </c>
+      <c r="C104" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="H102" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I102" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="52" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
-      <c r="A103" s="32"/>
-      <c r="B103" s="36"/>
-      <c r="C103" s="40"/>
-      <c r="D103" s="44"/>
-      <c r="E103" s="48"/>
-      <c r="F103" s="48"/>
-      <c r="G103" s="20" t="s">
+      <c r="D104" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E104" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="H103" s="50"/>
-      <c r="I103" s="48"/>
-      <c r="J103" s="53"/>
-    </row>
-    <row r="104" spans="1:10">
-      <c r="A104" s="32"/>
-      <c r="B104" s="36"/>
-      <c r="C104" s="40"/>
-      <c r="D104" s="44"/>
-      <c r="E104" s="48"/>
-      <c r="F104" s="48"/>
-      <c r="G104" s="20" t="s">
+      <c r="F104" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="H104" s="50"/>
-      <c r="I104" s="48"/>
-      <c r="J104" s="53"/>
-    </row>
-    <row r="105" spans="1:10">
-      <c r="A105" s="32"/>
-      <c r="B105" s="36"/>
-      <c r="C105" s="40"/>
-      <c r="D105" s="44"/>
-      <c r="E105" s="48"/>
-      <c r="F105" s="48"/>
-      <c r="G105" s="20" t="s">
+      <c r="G104" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H104" t="s">
+        <v>17</v>
+      </c>
+      <c r="I104" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J104" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A105" s="16">
+        <v>46191</v>
+      </c>
+      <c r="B105" s="15">
+        <v>0.77152777777777781</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D105" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F105" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G105" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H105" t="s">
+        <v>17</v>
+      </c>
+      <c r="I105" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J105" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A106" s="16">
+        <v>46183</v>
+      </c>
+      <c r="B106" s="15">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D106" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F106" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="H105" s="50"/>
-      <c r="I105" s="48"/>
-      <c r="J105" s="53"/>
-    </row>
-    <row r="106" spans="1:10">
-      <c r="A106" s="33"/>
-      <c r="B106" s="37"/>
-      <c r="C106" s="41"/>
-      <c r="D106" s="45"/>
-      <c r="E106" s="49"/>
-      <c r="F106" s="49"/>
-      <c r="G106" s="22" t="s">
+      <c r="G106" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="H106" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J106" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="16">
+        <v>46189</v>
+      </c>
+      <c r="B107" s="15">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" s="19">
+        <v>9744</v>
+      </c>
+      <c r="E107" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="H106" s="50"/>
-      <c r="I106" s="49"/>
-      <c r="J106" s="54"/>
-    </row>
-    <row r="107" spans="1:10">
-      <c r="A107" s="30">
+      <c r="F107" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G107" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="H107" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J107" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="16">
+        <v>46184</v>
+      </c>
+      <c r="B108" s="15">
+        <v>0.38055555555555554</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D108" s="19">
+        <v>9744</v>
+      </c>
+      <c r="E108" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="F108" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G108" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H108" t="s">
+        <v>17</v>
+      </c>
+      <c r="I108" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J108" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A109" s="16">
+        <v>46184</v>
+      </c>
+      <c r="B109" s="15">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D109" s="19">
+        <v>9759</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G109" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="H109" t="s">
+        <v>17</v>
+      </c>
+      <c r="I109" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="28.5">
+      <c r="A110" s="16">
+        <v>46185</v>
+      </c>
+      <c r="B110" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D110" s="19">
+        <v>9762</v>
+      </c>
+      <c r="E110" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F110" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G110" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H110" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="28.5">
+      <c r="A111" s="16">
         <v>46186</v>
       </c>
-      <c r="B107" s="34">
-        <v>0.47152777777777777</v>
-      </c>
-      <c r="C107" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="D107" s="42">
-        <v>81685</v>
-      </c>
-      <c r="E107" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="F107" s="46" t="s">
+      <c r="B111" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D111" s="19">
+        <v>9764</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F111" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="G107" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="H107" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I107" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J107" s="51" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10">
-      <c r="A108" s="32"/>
-      <c r="B108" s="36"/>
-      <c r="C108" s="40"/>
-      <c r="D108" s="44"/>
-      <c r="E108" s="48"/>
-      <c r="F108" s="48"/>
-      <c r="G108" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="H108" s="50"/>
-      <c r="I108" s="48"/>
-      <c r="J108" s="53"/>
-    </row>
-    <row r="109" spans="1:10">
-      <c r="A109" s="32"/>
-      <c r="B109" s="36"/>
-      <c r="C109" s="40"/>
-      <c r="D109" s="44"/>
-      <c r="E109" s="48"/>
-      <c r="F109" s="48"/>
-      <c r="G109" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="H109" s="50"/>
-      <c r="I109" s="48"/>
-      <c r="J109" s="53"/>
-    </row>
-    <row r="110" spans="1:10">
-      <c r="A110" s="32"/>
-      <c r="B110" s="36"/>
-      <c r="C110" s="40"/>
-      <c r="D110" s="44"/>
-      <c r="E110" s="48"/>
-      <c r="F110" s="48"/>
-      <c r="G110" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="H110" s="50"/>
-      <c r="I110" s="48"/>
-      <c r="J110" s="53"/>
-    </row>
-    <row r="111" spans="1:10">
-      <c r="A111" s="33"/>
-      <c r="B111" s="37"/>
-      <c r="C111" s="41"/>
-      <c r="D111" s="45"/>
-      <c r="E111" s="49"/>
-      <c r="F111" s="49"/>
-      <c r="G111" s="22"/>
-      <c r="H111" s="50"/>
-      <c r="I111" s="49"/>
-      <c r="J111" s="54"/>
-    </row>
-    <row r="112" spans="1:10">
-      <c r="A112" s="30">
-        <v>46190</v>
-      </c>
-      <c r="B112" s="34">
-        <v>0.77152777777777781</v>
-      </c>
-      <c r="C112" s="38" t="s">
+      <c r="G111" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H111" t="s">
+        <v>17</v>
+      </c>
+      <c r="I111" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="28.5">
+      <c r="A112" s="16">
+        <v>46186</v>
+      </c>
+      <c r="B112" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C112" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="D112" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E112" s="46" t="s">
+      <c r="D112" s="19">
+        <v>9764</v>
+      </c>
+      <c r="E112" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="F112" s="46" t="s">
-        <v>163</v>
-      </c>
-      <c r="G112" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="H112" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I112" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J112" s="51" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10">
-      <c r="A113" s="32"/>
-      <c r="B113" s="36"/>
-      <c r="C113" s="40"/>
-      <c r="D113" s="44"/>
-      <c r="E113" s="48"/>
-      <c r="F113" s="48"/>
-      <c r="G113" s="19"/>
-      <c r="H113" s="50"/>
-      <c r="I113" s="48"/>
-      <c r="J113" s="53"/>
-    </row>
-    <row r="114" spans="1:10">
-      <c r="A114" s="32"/>
-      <c r="B114" s="36"/>
-      <c r="C114" s="40"/>
-      <c r="D114" s="44"/>
-      <c r="E114" s="48"/>
-      <c r="F114" s="48"/>
-      <c r="G114" s="19"/>
-      <c r="H114" s="50"/>
-      <c r="I114" s="48"/>
-      <c r="J114" s="53"/>
-    </row>
-    <row r="115" spans="1:10">
-      <c r="A115" s="32"/>
-      <c r="B115" s="36"/>
-      <c r="C115" s="40"/>
-      <c r="D115" s="44"/>
-      <c r="E115" s="48"/>
-      <c r="F115" s="48"/>
-      <c r="G115" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="H115" s="50"/>
-      <c r="I115" s="48"/>
-      <c r="J115" s="53"/>
-    </row>
-    <row r="116" spans="1:10">
-      <c r="A116" s="33"/>
-      <c r="B116" s="37"/>
-      <c r="C116" s="41"/>
-      <c r="D116" s="45"/>
-      <c r="E116" s="49"/>
-      <c r="F116" s="49"/>
-      <c r="G116" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="H116" s="50"/>
-      <c r="I116" s="49"/>
-      <c r="J116" s="54"/>
-    </row>
-    <row r="117" spans="1:10">
-      <c r="A117" s="30">
-        <v>46191</v>
-      </c>
-      <c r="B117" s="34">
-        <v>0.77152777777777781</v>
-      </c>
-      <c r="C117" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="D117" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E117" s="46" t="s">
-        <v>162</v>
-      </c>
-      <c r="F117" s="46" t="s">
-        <v>163</v>
-      </c>
-      <c r="G117" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="H117" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I117" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" s="51" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
-      <c r="A118" s="32"/>
-      <c r="B118" s="36"/>
-      <c r="C118" s="40"/>
-      <c r="D118" s="44"/>
-      <c r="E118" s="48"/>
-      <c r="F118" s="48"/>
-      <c r="G118" s="19"/>
-      <c r="H118" s="50"/>
-      <c r="I118" s="48"/>
-      <c r="J118" s="53"/>
-    </row>
-    <row r="119" spans="1:10">
-      <c r="A119" s="32"/>
-      <c r="B119" s="36"/>
-      <c r="C119" s="40"/>
-      <c r="D119" s="44"/>
-      <c r="E119" s="48"/>
-      <c r="F119" s="48"/>
-      <c r="G119" s="19"/>
-      <c r="H119" s="50"/>
-      <c r="I119" s="48"/>
-      <c r="J119" s="53"/>
-    </row>
-    <row r="120" spans="1:10">
-      <c r="A120" s="32"/>
-      <c r="B120" s="36"/>
-      <c r="C120" s="40"/>
-      <c r="D120" s="44"/>
-      <c r="E120" s="48"/>
-      <c r="F120" s="48"/>
-      <c r="G120" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="H120" s="50"/>
-      <c r="I120" s="48"/>
-      <c r="J120" s="53"/>
-    </row>
-    <row r="121" spans="1:10">
-      <c r="A121" s="33"/>
-      <c r="B121" s="37"/>
-      <c r="C121" s="41"/>
-      <c r="D121" s="45"/>
-      <c r="E121" s="49"/>
-      <c r="F121" s="49"/>
-      <c r="G121" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="H121" s="50"/>
-      <c r="I121" s="49"/>
-      <c r="J121" s="54"/>
-    </row>
-    <row r="122" spans="1:10" ht="28.5">
-      <c r="A122" s="30">
-        <v>46183</v>
-      </c>
-      <c r="B122" s="34">
-        <v>0.77916666666666667</v>
-      </c>
-      <c r="C122" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="D122" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E122" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="F122" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="G122" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="H122" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I122" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J122" s="51" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
-      <c r="A123" s="32"/>
-      <c r="B123" s="36"/>
-      <c r="C123" s="40"/>
-      <c r="D123" s="44"/>
-      <c r="E123" s="48"/>
-      <c r="F123" s="48"/>
-      <c r="G123" s="20" t="s">
+      <c r="F112" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G112" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="H123" s="50"/>
-      <c r="I123" s="48"/>
-      <c r="J123" s="53"/>
-    </row>
-    <row r="124" spans="1:10">
-      <c r="A124" s="32"/>
-      <c r="B124" s="36"/>
-      <c r="C124" s="40"/>
-      <c r="D124" s="44"/>
-      <c r="E124" s="48"/>
-      <c r="F124" s="48"/>
-      <c r="G124" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="H124" s="50"/>
-      <c r="I124" s="48"/>
-      <c r="J124" s="53"/>
-    </row>
-    <row r="125" spans="1:10">
-      <c r="A125" s="32"/>
-      <c r="B125" s="36"/>
-      <c r="C125" s="40"/>
-      <c r="D125" s="44"/>
-      <c r="E125" s="48"/>
-      <c r="F125" s="48"/>
-      <c r="G125" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="H125" s="50"/>
-      <c r="I125" s="48"/>
-      <c r="J125" s="53"/>
-    </row>
-    <row r="126" spans="1:10">
-      <c r="A126" s="33"/>
-      <c r="B126" s="37"/>
-      <c r="C126" s="41"/>
-      <c r="D126" s="45"/>
-      <c r="E126" s="49"/>
-      <c r="F126" s="49"/>
-      <c r="G126" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="H126" s="50"/>
-      <c r="I126" s="49"/>
-      <c r="J126" s="54"/>
-    </row>
-    <row r="127" spans="1:10" ht="57">
-      <c r="A127" s="24">
-        <v>46189</v>
-      </c>
-      <c r="B127" s="25">
-        <v>0.77916666666666667</v>
-      </c>
-      <c r="C127" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="D127" s="27">
-        <v>9744</v>
-      </c>
-      <c r="E127" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="F127" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="G127" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="H127" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="I127" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J127" s="29" t="s">
+      <c r="H112" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" s="13" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="H122:H126"/>
-    <mergeCell ref="I122:I126"/>
-    <mergeCell ref="J122:J126"/>
-    <mergeCell ref="A122:A126"/>
-    <mergeCell ref="B122:B126"/>
-    <mergeCell ref="C122:C126"/>
-    <mergeCell ref="D122:D126"/>
-    <mergeCell ref="E122:E126"/>
-    <mergeCell ref="F122:F126"/>
-    <mergeCell ref="J112:J116"/>
-    <mergeCell ref="A117:A121"/>
-    <mergeCell ref="B117:B121"/>
-    <mergeCell ref="C117:C121"/>
-    <mergeCell ref="D117:D121"/>
-    <mergeCell ref="E117:E121"/>
-    <mergeCell ref="F117:F121"/>
-    <mergeCell ref="H117:H121"/>
-    <mergeCell ref="I117:I121"/>
-    <mergeCell ref="J117:J121"/>
-    <mergeCell ref="I107:I111"/>
-    <mergeCell ref="J107:J111"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="D112:D116"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="F112:F116"/>
-    <mergeCell ref="H112:H116"/>
-    <mergeCell ref="I112:I116"/>
-    <mergeCell ref="H102:H106"/>
-    <mergeCell ref="I102:I106"/>
-    <mergeCell ref="J102:J106"/>
-    <mergeCell ref="A107:A111"/>
-    <mergeCell ref="B107:B111"/>
-    <mergeCell ref="C107:C111"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="E107:E111"/>
-    <mergeCell ref="F107:F111"/>
-    <mergeCell ref="H107:H111"/>
-    <mergeCell ref="A102:A106"/>
-    <mergeCell ref="B102:B106"/>
-    <mergeCell ref="C102:C106"/>
-    <mergeCell ref="D102:D106"/>
-    <mergeCell ref="E102:E106"/>
-    <mergeCell ref="F102:F106"/>
-  </mergeCells>
-  <conditionalFormatting sqref="H2:H101">
+  <conditionalFormatting sqref="H2:H112">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>
@@ -5061,7 +4632,7 @@
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J101">
+  <conditionalFormatting sqref="J2:J112">
     <cfRule type="expression" dxfId="1" priority="4">
       <formula>J2="Ejecutado"</formula>
     </cfRule>
@@ -5160,14 +4731,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">
